--- a/assets/constructions/examples/ctd_mthr.xlsx
+++ b/assets/constructions/examples/ctd_mthr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,11 +674,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HTCM10X1.5X2.5DVTN</t>
+          <t>HTCM8X1.25X2.5DVTN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -704,7 +729,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>M10x1.5.5</t>
+          <t>M8x1.25.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,23 +743,23 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>M10x1.5.5</t>
+          <t>M8x1.25.5</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -746,36 +771,36 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>8.08</v>
+        <v>6.45</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>25.1</v>
+        <v>20.8</v>
       </c>
       <c r="X2" t="n">
-        <v>27.9</v>
+        <v>23.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>45</v>
       </c>
       <c r="AE2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
         <v>140</v>
@@ -810,7 +835,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,26 +860,45 @@
         </is>
       </c>
       <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>622.63</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>57240.68</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>KN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GTM315001 WU12PV</t>
+          <t>HTCM12X1.75X2DVTS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GTM31</t>
+          <t>Helicool</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -865,7 +909,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>M4X0,7</t>
+          <t>M12x1.75</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -879,19 +923,23 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.75</v>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>M4X0,7</t>
+          <t>M12x1.75</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -903,40 +951,36 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3.2</v>
+        <v>9.74</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>7.74</v>
+        <v>24</v>
       </c>
       <c r="X3" t="n">
-        <v>9.59</v>
+        <v>27.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>10.3</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="AB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.85</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>45</v>
       </c>
       <c r="AE3" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="AF3" t="n">
         <v>140</v>
@@ -949,13 +993,13 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>WU12PV</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -971,7 +1015,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -981,7 +1025,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr"/>
@@ -992,15 +1036,34 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2017/Widia Метчикии резьбофрезы</t>
+          <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1112.75</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
+        <v>102299.22</v>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HTCM10X1.5X2DVTN</t>
+          <t>HTCM10X1.5X2.5DVTS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1015,7 +1078,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1026,7 +1089,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M10x1.5</t>
+          <t>M10x1.5.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1056,7 +1119,7 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>M10x1.5</t>
+          <t>M10x1.5.5</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1075,10 +1138,10 @@
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>20.6</v>
+        <v>25.1</v>
       </c>
       <c r="X4" t="n">
-        <v>23.4</v>
+        <v>27.9</v>
       </c>
       <c r="Y4" t="n">
         <v>79</v>
@@ -1110,13 +1173,13 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>VTN</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1157,11 +1220,30 @@
         </is>
       </c>
       <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>829.65</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>76272.78999999999</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HTCM12X1.75X2DVTN</t>
+          <t>HTCM8X1.25X2DVTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1176,7 +1258,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1187,7 +1269,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M12x1.75</t>
+          <t>M8x1.25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1201,23 +1283,23 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>M12x1.75</t>
+          <t>M8x1.25</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1229,36 +1311,36 @@
         <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>9.74</v>
+        <v>6.45</v>
       </c>
       <c r="U5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>24</v>
+        <v>15.8</v>
       </c>
       <c r="X5" t="n">
-        <v>27.1</v>
+        <v>18.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.3</v>
+        <v>6.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>45</v>
       </c>
       <c r="AE5" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
         <v>140</v>
@@ -1271,13 +1353,13 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>VTN</t>
+          <t>VTS</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1293,7 +1375,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1318,11 +1400,30 @@
         </is>
       </c>
       <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>687.25</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
+        <v>63181.44</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HTCM10X1.5X2.5DVTS</t>
+          <t>HTCM6X1.0X2DVTN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1337,7 +1438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1348,7 +1449,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M10x1.5.5</t>
+          <t>M6x1.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1362,23 +1463,23 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>M10x1.5.5</t>
+          <t>M6x1.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1390,36 +1491,36 @@
         <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>8.08</v>
+        <v>4.85</v>
       </c>
       <c r="U6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>25.1</v>
+        <v>12.7</v>
       </c>
       <c r="X6" t="n">
-        <v>27.9</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.3</v>
+        <v>6.3</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>45</v>
       </c>
       <c r="AE6" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="AF6" t="n">
         <v>140</v>
@@ -1432,13 +1533,13 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>VTN</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1454,7 +1555,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1479,6 +1580,17 @@
         </is>
       </c>
       <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>KN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
